--- a/data/dividends_info_20260730.xlsx
+++ b/data/dividends_info_20260730.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.56499862670898</v>
+        <v>45.625</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2065878637370655</v>
+        <v>0.1972602739726027</v>
       </c>
       <c r="J2" t="n">
         <v>228</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.5</v>
+        <v>65.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.085271317829457</v>
+        <v>1.0727969348659</v>
       </c>
       <c r="J3" t="n">
         <v>207</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.039999961853027</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6637168169600428</v>
+        <v>0.6651884363083036</v>
       </c>
       <c r="J4" t="n">
         <v>137</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.56499862670898</v>
+        <v>45.625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2065878637370655</v>
+        <v>0.1972602739726027</v>
       </c>
       <c r="J6" t="n">
         <v>137</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.109999895095825</v>
+        <v>2.105000019073486</v>
       </c>
       <c r="I7" t="n">
-        <v>3.649289280960038</v>
+        <v>3.65795721151069</v>
       </c>
       <c r="J7" t="n">
         <v>116</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.6200008392334</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="I8" t="n">
-        <v>1.143099027970919</v>
+        <v>1.129707131002053</v>
       </c>
       <c r="J8" t="n">
         <v>116</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.019999980926514</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I9" t="n">
-        <v>3.322259146738715</v>
+        <v>3.350083869828403</v>
       </c>
       <c r="J9" t="n">
         <v>109</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.199999809265137</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8333333554091283</v>
+        <v>0.7947019666784939</v>
       </c>
       <c r="J10" t="n">
         <v>81</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.039999961853027</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I13" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7421875165891837</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.6200008392334</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="I14" t="n">
-        <v>1.143099027970919</v>
+        <v>1.129707131002053</v>
       </c>
       <c r="J14" t="n">
         <v>53</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.032000064849854</v>
+        <v>1.985000014305115</v>
       </c>
       <c r="I15" t="n">
-        <v>2.805118020712848</v>
+        <v>2.871536503235436</v>
       </c>
       <c r="J15" t="n">
         <v>53</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>43.56499862670898</v>
+        <v>45.625</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2065878637370655</v>
+        <v>0.1972602739726027</v>
       </c>
       <c r="J16" t="n">
         <v>53</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>93.15000152587891</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="I17" t="n">
-        <v>1.427804592821719</v>
+        <v>1.42398284611536</v>
       </c>
       <c r="J17" t="n">
         <v>53</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.760000228881836</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I18" t="n">
-        <v>5.208333126372769</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J18" t="n">
         <v>46</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.799999952316284</v>
+        <v>2.779999971389771</v>
       </c>
       <c r="I20" t="n">
-        <v>7.857142990949205</v>
+        <v>7.913669146191328</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.039999961853027</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I21" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7421875165891837</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.029999971389771</v>
+        <v>3.049999952316284</v>
       </c>
       <c r="I23" t="n">
-        <v>4.883465392645896</v>
+        <v>4.8514426987983</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.659999847412109</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I24" t="n">
-        <v>4.416961249818869</v>
+        <v>4.370629530943106</v>
       </c>
       <c r="J24" t="n">
         <v>-3</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3.960000038146973</v>
+        <v>4.019999980926514</v>
       </c>
       <c r="I25" t="n">
-        <v>3.535353501297214</v>
+        <v>3.482587081200268</v>
       </c>
       <c r="J25" t="n">
         <v>-10</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9.855999946594238</v>
+        <v>9.842000007629395</v>
       </c>
       <c r="I26" t="n">
-        <v>2.63798702728122</v>
+        <v>2.641739481796904</v>
       </c>
       <c r="J26" t="n">
         <v>-10</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.96000003814697</v>
+        <v>13.65999984741211</v>
       </c>
       <c r="I27" t="n">
-        <v>4.297994257596313</v>
+        <v>4.392386579079429</v>
       </c>
       <c r="J27" t="n">
         <v>-10</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.619999885559082</v>
+        <v>2.584000110626221</v>
       </c>
       <c r="I28" t="n">
-        <v>8.396946931661953</v>
+        <v>8.513931524046413</v>
       </c>
       <c r="J28" t="n">
         <v>-10</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.349999904632568</v>
+        <v>6.510000228881836</v>
       </c>
       <c r="I30" t="n">
-        <v>3.779527615817928</v>
+        <v>3.686635815083875</v>
       </c>
       <c r="J30" t="n">
         <v>-10</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>18.60000038146973</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>2.02150533488478</v>
+        <v>2.06593397933063</v>
       </c>
       <c r="J31" t="n">
         <v>-10</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.799999952316284</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="I35" t="n">
-        <v>5.357142948374458</v>
+        <v>5.281690300468702</v>
       </c>
       <c r="J35" t="n">
         <v>-17</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.140000104904175</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I36" t="n">
-        <v>3.971962422114281</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J36" t="n">
         <v>-24</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.420000076293945</v>
+        <v>4.449999809265137</v>
       </c>
       <c r="I37" t="n">
-        <v>1.583710379903278</v>
+        <v>1.573033775288176</v>
       </c>
       <c r="J37" t="n">
         <v>-24</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>36</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4120878948132904</v>
       </c>
       <c r="J38" t="n">
         <v>-24</v>
@@ -4229,7 +4229,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4324,14 +4324,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4348,7 +4348,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4358,14 +4358,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4382,7 +4382,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4399,7 +4399,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4416,7 +4416,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4426,14 +4426,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4450,7 +4450,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4467,7 +4467,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4511,14 +4511,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4535,7 +4535,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4545,14 +4545,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4562,14 +4562,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4579,14 +4579,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4613,14 +4613,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4715,14 +4715,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4783,14 +4783,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4800,14 +4800,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
